--- a/Unsorted/Pushkin/разрушения/разрушения_подписи_пушкин.xlsx
+++ b/Unsorted/Pushkin/разрушения/разрушения_подписи_пушкин.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\Disk E\arhiv_site\Пушкин_выкладка\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\liferay-ce-portal-7.2.1-ga2\PeterhoffParts\Peterhoff\Unsorted\Pushkin\разрушения\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00875D86-DADB-4113-B3CA-0C5B122A3763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91CF12AF-5DE4-4181-9868-D776A1E2D235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21360" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5835" yWindow="3120" windowWidth="18540" windowHeight="11385" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -178,7 +178,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -460,13 +460,13 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="42.7265625" customWidth="1"/>
-    <col min="2" max="2" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="42.7109375" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -474,7 +474,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>4</v>
       </c>
@@ -482,7 +482,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -490,7 +490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -498,7 +498,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -506,7 +506,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -514,7 +514,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -522,7 +522,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -541,13 +541,13 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="42.90625" customWidth="1"/>
-    <col min="2" max="2" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="42.85546875" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -555,7 +555,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>4</v>
       </c>
@@ -563,7 +563,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -571,7 +571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -579,7 +579,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -587,7 +587,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -606,13 +606,13 @@
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="42.7265625" customWidth="1"/>
-    <col min="2" max="2" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="42.7109375" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -620,7 +620,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>5</v>
       </c>
@@ -628,7 +628,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -636,7 +636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -644,7 +644,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -652,7 +652,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
